--- a/surgical_staging/STAGED_CRS610MI_Customers.xlsx
+++ b/surgical_staging/STAGED_CRS610MI_Customers.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="282">
   <si>
     <t>OKCUNO</t>
   </si>
@@ -634,52 +634,31 @@
     <t>OKCHID</t>
   </si>
   <si>
-    <t xml:space="preserve">41973     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">44010     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summit Packaging Inc.               </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motts LLP                           </t>
+    <t xml:space="preserve">55402     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ken's Foods LLC - GA                </t>
   </si>
   <si>
     <t>20</t>
   </si>
   <si>
-    <t>0533</t>
-  </si>
-  <si>
-    <t>0737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1401 West Vally Hwy N.              </t>
-  </si>
-  <si>
-    <t xml:space="preserve">PO BOX 2287                         </t>
+    <t>0745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 D'angelo Drive                    </t>
   </si>
   <si>
     <t xml:space="preserve">                                    </t>
   </si>
   <si>
-    <t xml:space="preserve">Auburn, Wa 98001                    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frisco TX 75034                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fax 253-858-8181                    </t>
+    <t xml:space="preserve">Marlborough MA 01752                </t>
   </si>
   <si>
     <t xml:space="preserve">USA                                 </t>
   </si>
   <si>
-    <t>WA</t>
-  </si>
-  <si>
-    <t>TX</t>
+    <t>MA</t>
   </si>
   <si>
     <t>100.0</t>
@@ -688,211 +667,172 @@
     <t xml:space="preserve">   </t>
   </si>
   <si>
-    <t>72C</t>
-  </si>
-  <si>
-    <t>MOT</t>
+    <t>430</t>
   </si>
   <si>
     <t>0.0</t>
   </si>
   <si>
-    <t>SUMMIT PAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MOTTS     </t>
+    <t xml:space="preserve">KEN'S     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">001   </t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508-229-5498    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crystie Davis                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t>070</t>
+  </si>
+  <si>
+    <t>PPA</t>
+  </si>
+  <si>
+    <t>019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W65MKBHS  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HUSD01    </t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>H1</t>
+  </si>
+  <si>
+    <t>YMD</t>
+  </si>
+  <si>
+    <t>/</t>
+  </si>
+  <si>
+    <t>HMA</t>
+  </si>
+  <si>
+    <t>386</t>
+  </si>
+  <si>
+    <t>WHS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US </t>
+  </si>
+  <si>
+    <t xml:space="preserve">*  </t>
+  </si>
+  <si>
+    <t>GB</t>
+  </si>
+  <si>
+    <t>1100000.0</t>
+  </si>
+  <si>
+    <t>5.0</t>
+  </si>
+  <si>
+    <t>710609.34</t>
+  </si>
+  <si>
+    <t>563009.26</t>
+  </si>
+  <si>
+    <t>2890.44</t>
+  </si>
+  <si>
+    <t>20260724.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FOOD </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">01752     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KENSFOODS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">G40109    </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve">450       </t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>HSYUS</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">IN              </t>
+  </si>
+  <si>
+    <t>2.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W25MKMNN  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">W25ACCEG  </t>
+  </si>
+  <si>
+    <t>20211122.0</t>
+  </si>
+  <si>
+    <t>20250722.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                    </t>
   </si>
   <si>
     <t xml:space="preserve">      </t>
   </si>
   <si>
-    <t>1.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">253-858-4040    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">                </t>
-  </si>
-  <si>
-    <t xml:space="preserve">           </t>
-  </si>
-  <si>
-    <t xml:space="preserve">                              </t>
-  </si>
-  <si>
-    <t xml:space="preserve">          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  </t>
-  </si>
-  <si>
-    <t>070</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>COL</t>
-  </si>
-  <si>
-    <t>019</t>
-  </si>
-  <si>
-    <t>002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W41MKSNC  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">W41MKLSR  </t>
-  </si>
-  <si>
-    <t>99</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>USD</t>
-  </si>
-  <si>
-    <t>YMD</t>
-  </si>
-  <si>
-    <t>/</t>
-  </si>
-  <si>
-    <t>RWP</t>
-  </si>
-  <si>
-    <t>251</t>
-  </si>
-  <si>
-    <t>261</t>
-  </si>
-  <si>
-    <t>WPP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US </t>
-  </si>
-  <si>
-    <t>007</t>
-  </si>
-  <si>
-    <t>GB</t>
-  </si>
-  <si>
-    <t>25000.0</t>
-  </si>
-  <si>
-    <t>5.0</t>
-  </si>
-  <si>
-    <t>3642.3</t>
-  </si>
-  <si>
-    <t>20140715.0</t>
-  </si>
-  <si>
-    <t>20260413.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">FOOD </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0684 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">98335     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">G41973    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">G40072    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">WE   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">CE   </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t xml:space="preserve">360       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">432       </t>
-  </si>
-  <si>
-    <t>047</t>
-  </si>
-  <si>
-    <t>124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4         </t>
-  </si>
-  <si>
-    <t>2.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W35MKPRH  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">W41MKJHN  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">W35ACMES  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">W41ACSMP  </t>
-  </si>
-  <si>
-    <t>20080418.0</t>
-  </si>
-  <si>
-    <t>20251218.0</t>
-  </si>
-  <si>
-    <t>20101015.0</t>
-  </si>
-  <si>
-    <t>20260223.0</t>
-  </si>
-  <si>
-    <t>20260505.0</t>
-  </si>
-  <si>
-    <t>20260330.0</t>
-  </si>
-  <si>
-    <t>901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                    </t>
-  </si>
-  <si>
-    <t>*NA</t>
-  </si>
-  <si>
-    <t>060</t>
-  </si>
-  <si>
-    <t>1914763.0</t>
-  </si>
-  <si>
-    <t>4877200.0</t>
+    <t>4997777.0</t>
+  </si>
+  <si>
+    <t>H001</t>
   </si>
   <si>
     <t xml:space="preserve">    </t>
@@ -901,13 +841,7 @@
     <t>6.0</t>
   </si>
   <si>
-    <t>15.0</t>
-  </si>
-  <si>
-    <t>500100001.0</t>
-  </si>
-  <si>
-    <t>140000000.0</t>
+    <t>76.0</t>
   </si>
   <si>
     <t xml:space="preserve">                  </t>
@@ -919,22 +853,13 @@
     <t xml:space="preserve">                                </t>
   </si>
   <si>
-    <t>001</t>
-  </si>
-  <si>
-    <t>104625.0</t>
-  </si>
-  <si>
-    <t>95933.0</t>
-  </si>
-  <si>
-    <t>20260430.0</t>
-  </si>
-  <si>
-    <t>641.0</t>
-  </si>
-  <si>
-    <t>990.0</t>
+    <t>120250.0</t>
+  </si>
+  <si>
+    <t>20260714.0</t>
+  </si>
+  <si>
+    <t>148.0</t>
   </si>
 </sst>
 </file>
@@ -1292,7 +1217,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:GX3"/>
+  <dimension ref="A1:GX2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:206">
@@ -1920,1239 +1845,619 @@
         <v>206</v>
       </c>
       <c r="B2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C2" t="s">
         <v>208</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E2" t="s">
         <v>210</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>211</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H2" t="s">
         <v>213</v>
       </c>
-      <c r="F2" t="s">
+      <c r="I2" t="s">
+        <v>214</v>
+      </c>
+      <c r="J2" t="s">
         <v>215</v>
       </c>
-      <c r="G2" t="s">
+      <c r="K2" t="s">
         <v>216</v>
       </c>
-      <c r="H2" t="s">
-        <v>218</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="L2" t="s">
+        <v>217</v>
+      </c>
+      <c r="M2" t="s">
+        <v>218</v>
+      </c>
+      <c r="N2" t="s">
+        <v>219</v>
+      </c>
+      <c r="O2" t="s">
         <v>220</v>
       </c>
-      <c r="J2" t="s">
+      <c r="P2" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q2" t="s">
         <v>222</v>
       </c>
-      <c r="K2" t="s">
+      <c r="R2" t="s">
         <v>223</v>
       </c>
-      <c r="L2" t="s">
+      <c r="S2" t="s">
+        <v>223</v>
+      </c>
+      <c r="T2" t="s">
         <v>224</v>
       </c>
-      <c r="M2" t="s">
+      <c r="U2" t="s">
+        <v>224</v>
+      </c>
+      <c r="V2" t="s">
+        <v>225</v>
+      </c>
+      <c r="W2" t="s">
         <v>226</v>
       </c>
-      <c r="N2" t="s">
+      <c r="X2" t="s">
+        <v>226</v>
+      </c>
+      <c r="Y2" t="s">
         <v>227</v>
       </c>
-      <c r="O2" t="s">
+      <c r="Z2" t="s">
+        <v>228</v>
+      </c>
+      <c r="AA2" t="s">
         <v>229</v>
       </c>
-      <c r="P2" t="s">
+      <c r="AB2" t="s">
+        <v>218</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>216</v>
+      </c>
+      <c r="AD2" t="s">
         <v>230</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="AE2" t="s">
         <v>231</v>
       </c>
-      <c r="R2" t="s">
+      <c r="AF2" t="s">
         <v>232</v>
       </c>
-      <c r="S2" t="s">
-        <v>232</v>
-      </c>
-      <c r="T2" t="s">
+      <c r="AG2" t="s">
+        <v>216</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>218</v>
+      </c>
+      <c r="AI2" t="s">
         <v>233</v>
       </c>
-      <c r="U2" t="s">
-        <v>233</v>
-      </c>
-      <c r="V2" t="s">
+      <c r="AJ2" t="s">
+        <v>228</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>218</v>
+      </c>
+      <c r="AL2" t="s">
         <v>234</v>
       </c>
-      <c r="W2" t="s">
-        <v>234</v>
-      </c>
-      <c r="X2" t="s">
-        <v>234</v>
-      </c>
-      <c r="Y2" t="s">
+      <c r="AM2" t="s">
         <v>235</v>
       </c>
-      <c r="Z2" t="s">
-        <v>236</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>237</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>226</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>223</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>239</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>240</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>242</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>223</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>226</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>235</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>236</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>226</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>244</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>246</v>
-      </c>
       <c r="AN2" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="AO2" t="s">
         <v>236</v>
       </c>
       <c r="AP2" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="AQ2" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="AR2" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="AS2" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="AT2" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="AU2" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="AV2" t="s">
+        <v>237</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>238</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>239</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>240</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>221</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>241</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>242</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>227</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>227</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>227</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>227</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>227</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>227</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>227</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>227</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>227</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>227</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>243</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>244</v>
+      </c>
+      <c r="BO2" t="s">
+        <v>218</v>
+      </c>
+      <c r="BP2" t="s">
+        <v>218</v>
+      </c>
+      <c r="BQ2" t="s">
+        <v>245</v>
+      </c>
+      <c r="BR2" t="s">
+        <v>218</v>
+      </c>
+      <c r="BS2" t="s">
+        <v>246</v>
+      </c>
+      <c r="BT2" t="s">
         <v>247</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="BU2" t="s">
         <v>248</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="BV2" t="s">
         <v>249</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="BW2" t="s">
         <v>250</v>
       </c>
-      <c r="AZ2" t="s">
-        <v>230</v>
-      </c>
-      <c r="BA2" t="s">
+      <c r="BX2" t="s">
+        <v>218</v>
+      </c>
+      <c r="BY2" t="s">
+        <v>251</v>
+      </c>
+      <c r="BZ2" t="s">
+        <v>218</v>
+      </c>
+      <c r="CA2" t="s">
+        <v>218</v>
+      </c>
+      <c r="CB2" t="s">
         <v>252</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="CC2" t="s">
         <v>253</v>
       </c>
-      <c r="BC2" t="s">
-        <v>235</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>235</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>235</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>235</v>
-      </c>
-      <c r="BG2" t="s">
-        <v>235</v>
-      </c>
-      <c r="BH2" t="s">
-        <v>235</v>
-      </c>
-      <c r="BI2" t="s">
-        <v>235</v>
-      </c>
-      <c r="BJ2" t="s">
-        <v>235</v>
-      </c>
-      <c r="BK2" t="s">
-        <v>235</v>
-      </c>
-      <c r="BL2" t="s">
-        <v>235</v>
-      </c>
-      <c r="BM2" t="s">
+      <c r="CD2" t="s">
+        <v>228</v>
+      </c>
+      <c r="CE2" t="s">
+        <v>242</v>
+      </c>
+      <c r="CF2" t="s">
+        <v>218</v>
+      </c>
+      <c r="CG2" t="s">
+        <v>216</v>
+      </c>
+      <c r="CH2" t="s">
+        <v>218</v>
+      </c>
+      <c r="CI2" t="s">
+        <v>218</v>
+      </c>
+      <c r="CJ2" t="s">
+        <v>216</v>
+      </c>
+      <c r="CK2" t="s">
+        <v>218</v>
+      </c>
+      <c r="CL2" t="s">
+        <v>216</v>
+      </c>
+      <c r="CM2" t="s">
+        <v>216</v>
+      </c>
+      <c r="CN2" t="s">
         <v>254</v>
       </c>
-      <c r="BN2" t="s">
+      <c r="CO2" t="s">
+        <v>218</v>
+      </c>
+      <c r="CP2" t="s">
+        <v>218</v>
+      </c>
+      <c r="CQ2" t="s">
         <v>255</v>
       </c>
-      <c r="BO2" t="s">
+      <c r="CR2" t="s">
+        <v>218</v>
+      </c>
+      <c r="CS2" t="s">
+        <v>218</v>
+      </c>
+      <c r="CT2" t="s">
+        <v>218</v>
+      </c>
+      <c r="CU2" t="s">
+        <v>218</v>
+      </c>
+      <c r="CV2" t="s">
+        <v>218</v>
+      </c>
+      <c r="CW2" t="s">
+        <v>218</v>
+      </c>
+      <c r="CX2" t="s">
+        <v>218</v>
+      </c>
+      <c r="CY2" t="s">
+        <v>256</v>
+      </c>
+      <c r="CZ2" t="s">
+        <v>218</v>
+      </c>
+      <c r="DA2" t="s">
+        <v>216</v>
+      </c>
+      <c r="DB2" t="s">
+        <v>253</v>
+      </c>
+      <c r="DC2" t="s">
+        <v>257</v>
+      </c>
+      <c r="DD2" t="s">
+        <v>258</v>
+      </c>
+      <c r="DE2" t="s">
+        <v>218</v>
+      </c>
+      <c r="DF2" t="s">
+        <v>259</v>
+      </c>
+      <c r="DG2" t="s">
+        <v>260</v>
+      </c>
+      <c r="DH2" t="s">
+        <v>261</v>
+      </c>
+      <c r="DI2" t="s">
+        <v>251</v>
+      </c>
+      <c r="DJ2" t="s">
+        <v>251</v>
+      </c>
+      <c r="DK2" t="s">
+        <v>262</v>
+      </c>
+      <c r="DL2" t="s">
+        <v>263</v>
+      </c>
+      <c r="DM2" t="s">
+        <v>264</v>
+      </c>
+      <c r="DN2" t="s">
+        <v>264</v>
+      </c>
+      <c r="DO2" t="s">
+        <v>221</v>
+      </c>
+      <c r="DP2" t="s">
+        <v>265</v>
+      </c>
+      <c r="DQ2" t="s">
+        <v>265</v>
+      </c>
+      <c r="DR2" t="s">
+        <v>266</v>
+      </c>
+      <c r="DS2" t="s">
+        <v>267</v>
+      </c>
+      <c r="DT2" t="s">
+        <v>267</v>
+      </c>
+      <c r="DU2" t="s">
+        <v>268</v>
+      </c>
+      <c r="DV2" t="s">
+        <v>216</v>
+      </c>
+      <c r="DW2" t="s">
+        <v>227</v>
+      </c>
+      <c r="DX2" t="s">
+        <v>269</v>
+      </c>
+      <c r="DY2" t="s">
+        <v>227</v>
+      </c>
+      <c r="DZ2" t="s">
+        <v>218</v>
+      </c>
+      <c r="EA2" t="s">
+        <v>218</v>
+      </c>
+      <c r="EB2" t="s">
+        <v>218</v>
+      </c>
+      <c r="EC2" t="s">
+        <v>227</v>
+      </c>
+      <c r="ED2" t="s">
+        <v>218</v>
+      </c>
+      <c r="EE2" t="s">
+        <v>218</v>
+      </c>
+      <c r="EF2" t="s">
+        <v>227</v>
+      </c>
+      <c r="EG2" t="s">
+        <v>228</v>
+      </c>
+      <c r="EH2" t="s">
+        <v>216</v>
+      </c>
+      <c r="EI2" t="s">
+        <v>270</v>
+      </c>
+      <c r="EJ2" t="s">
+        <v>218</v>
+      </c>
+      <c r="EK2" t="s">
+        <v>253</v>
+      </c>
+      <c r="EL2" t="s">
+        <v>228</v>
+      </c>
+      <c r="EM2" t="s">
+        <v>253</v>
+      </c>
+      <c r="EN2" t="s">
+        <v>253</v>
+      </c>
+      <c r="EO2" t="s">
+        <v>253</v>
+      </c>
+      <c r="EP2" t="s">
+        <v>253</v>
+      </c>
+      <c r="EQ2" t="s">
+        <v>253</v>
+      </c>
+      <c r="ER2" t="s">
+        <v>216</v>
+      </c>
+      <c r="ES2" t="s">
+        <v>218</v>
+      </c>
+      <c r="ET2" t="s">
+        <v>271</v>
+      </c>
+      <c r="EU2" t="s">
+        <v>218</v>
+      </c>
+      <c r="EV2" t="s">
+        <v>272</v>
+      </c>
+      <c r="EW2" t="s">
+        <v>273</v>
+      </c>
+      <c r="EX2" t="s">
+        <v>218</v>
+      </c>
+      <c r="EY2" t="s">
+        <v>218</v>
+      </c>
+      <c r="EZ2" t="s">
+        <v>218</v>
+      </c>
+      <c r="FA2" t="s">
+        <v>228</v>
+      </c>
+      <c r="FB2" t="s">
+        <v>216</v>
+      </c>
+      <c r="FC2" t="s">
+        <v>218</v>
+      </c>
+      <c r="FD2" t="s">
+        <v>227</v>
+      </c>
+      <c r="FE2" t="s">
+        <v>221</v>
+      </c>
+      <c r="FF2" t="s">
+        <v>218</v>
+      </c>
+      <c r="FG2" t="s">
+        <v>218</v>
+      </c>
+      <c r="FH2" t="s">
+        <v>218</v>
+      </c>
+      <c r="FI2" t="s">
+        <v>221</v>
+      </c>
+      <c r="FJ2" t="s">
+        <v>218</v>
+      </c>
+      <c r="FK2" t="s">
+        <v>218</v>
+      </c>
+      <c r="FL2" t="s">
+        <v>274</v>
+      </c>
+      <c r="FM2" t="s">
         <v>226</v>
       </c>
-      <c r="BP2" t="s">
-        <v>226</v>
-      </c>
-      <c r="BQ2" t="s">
-        <v>256</v>
-      </c>
-      <c r="BR2" t="s">
-        <v>226</v>
-      </c>
-      <c r="BS2" t="s">
-        <v>257</v>
-      </c>
-      <c r="BT2" t="s">
-        <v>226</v>
-      </c>
-      <c r="BU2" t="s">
-        <v>226</v>
-      </c>
-      <c r="BV2" t="s">
-        <v>226</v>
-      </c>
-      <c r="BW2" t="s">
-        <v>259</v>
-      </c>
-      <c r="BX2" t="s">
-        <v>226</v>
-      </c>
-      <c r="BY2" t="s">
-        <v>261</v>
-      </c>
-      <c r="BZ2" t="s">
-        <v>226</v>
-      </c>
-      <c r="CA2" t="s">
-        <v>226</v>
-      </c>
-      <c r="CB2" t="s">
-        <v>262</v>
-      </c>
-      <c r="CC2" t="s">
-        <v>262</v>
-      </c>
-      <c r="CD2" t="s">
-        <v>236</v>
-      </c>
-      <c r="CE2" t="s">
+      <c r="FN2" t="s">
+        <v>218</v>
+      </c>
+      <c r="FO2" t="s">
+        <v>228</v>
+      </c>
+      <c r="FP2" t="s">
+        <v>228</v>
+      </c>
+      <c r="FQ2" t="s">
+        <v>228</v>
+      </c>
+      <c r="FR2" t="s">
+        <v>228</v>
+      </c>
+      <c r="FS2" t="s">
+        <v>228</v>
+      </c>
+      <c r="FT2" t="s">
+        <v>227</v>
+      </c>
+      <c r="FU2" t="s">
+        <v>218</v>
+      </c>
+      <c r="FV2" t="s">
+        <v>218</v>
+      </c>
+      <c r="FW2" t="s">
+        <v>275</v>
+      </c>
+      <c r="FX2" t="s">
+        <v>218</v>
+      </c>
+      <c r="FY2" t="s">
+        <v>218</v>
+      </c>
+      <c r="FZ2" t="s">
+        <v>269</v>
+      </c>
+      <c r="GA2" t="s">
+        <v>218</v>
+      </c>
+      <c r="GB2" t="s">
+        <v>276</v>
+      </c>
+      <c r="GC2" t="s">
         <v>253</v>
       </c>
-      <c r="CF2" t="s">
-        <v>226</v>
-      </c>
-      <c r="CG2" t="s">
+      <c r="GD2" t="s">
+        <v>277</v>
+      </c>
+      <c r="GE2" t="s">
         <v>223</v>
       </c>
-      <c r="CH2" t="s">
-        <v>226</v>
-      </c>
-      <c r="CI2" t="s">
-        <v>226</v>
-      </c>
-      <c r="CJ2" t="s">
-        <v>223</v>
-      </c>
-      <c r="CK2" t="s">
-        <v>226</v>
-      </c>
-      <c r="CL2" t="s">
-        <v>223</v>
-      </c>
-      <c r="CM2" t="s">
-        <v>223</v>
-      </c>
-      <c r="CN2" t="s">
-        <v>265</v>
-      </c>
-      <c r="CO2" t="s">
-        <v>226</v>
-      </c>
-      <c r="CP2" t="s">
-        <v>226</v>
-      </c>
-      <c r="CQ2" t="s">
-        <v>235</v>
-      </c>
-      <c r="CR2" t="s">
-        <v>226</v>
-      </c>
-      <c r="CS2" t="s">
-        <v>226</v>
-      </c>
-      <c r="CT2" t="s">
-        <v>226</v>
-      </c>
-      <c r="CU2" t="s">
-        <v>226</v>
-      </c>
-      <c r="CV2" t="s">
-        <v>226</v>
-      </c>
-      <c r="CW2" t="s">
-        <v>226</v>
-      </c>
-      <c r="CX2" t="s">
-        <v>226</v>
-      </c>
-      <c r="CY2" t="s">
-        <v>266</v>
-      </c>
-      <c r="CZ2" t="s">
-        <v>226</v>
-      </c>
-      <c r="DA2" t="s">
-        <v>223</v>
-      </c>
-      <c r="DB2" t="s">
-        <v>268</v>
-      </c>
-      <c r="DC2" t="s">
+      <c r="GF2" t="s">
+        <v>273</v>
+      </c>
+      <c r="GG2" t="s">
+        <v>277</v>
+      </c>
+      <c r="GH2" t="s">
+        <v>277</v>
+      </c>
+      <c r="GI2" t="s">
+        <v>218</v>
+      </c>
+      <c r="GJ2" t="s">
+        <v>218</v>
+      </c>
+      <c r="GK2" t="s">
+        <v>218</v>
+      </c>
+      <c r="GL2" t="s">
+        <v>218</v>
+      </c>
+      <c r="GM2" t="s">
+        <v>218</v>
+      </c>
+      <c r="GN2" t="s">
+        <v>227</v>
+      </c>
+      <c r="GO2" t="s">
+        <v>278</v>
+      </c>
+      <c r="GP2" t="s">
+        <v>227</v>
+      </c>
+      <c r="GQ2" t="s">
+        <v>216</v>
+      </c>
+      <c r="GR2" t="s">
         <v>270</v>
       </c>
-      <c r="DD2" t="s">
-        <v>271</v>
-      </c>
-      <c r="DE2" t="s">
-        <v>226</v>
-      </c>
-      <c r="DF2" t="s">
-        <v>273</v>
-      </c>
-      <c r="DG2" t="s">
-        <v>262</v>
-      </c>
-      <c r="DH2" t="s">
-        <v>270</v>
-      </c>
-      <c r="DI2" t="s">
-        <v>261</v>
-      </c>
-      <c r="DJ2" t="s">
-        <v>261</v>
-      </c>
-      <c r="DK2" t="s">
-        <v>235</v>
-      </c>
-      <c r="DL2" t="s">
+      <c r="GS2" t="s">
+        <v>218</v>
+      </c>
+      <c r="GT2" t="s">
+        <v>267</v>
+      </c>
+      <c r="GU2" t="s">
+        <v>279</v>
+      </c>
+      <c r="GV2" t="s">
+        <v>280</v>
+      </c>
+      <c r="GW2" t="s">
+        <v>281</v>
+      </c>
+      <c r="GX2" t="s">
         <v>232</v>
-      </c>
-      <c r="DM2" t="s">
-        <v>276</v>
-      </c>
-      <c r="DN2" t="s">
-        <v>276</v>
-      </c>
-      <c r="DO2" t="s">
-        <v>230</v>
-      </c>
-      <c r="DP2" t="s">
-        <v>277</v>
-      </c>
-      <c r="DQ2" t="s">
-        <v>279</v>
-      </c>
-      <c r="DR2" t="s">
-        <v>280</v>
-      </c>
-      <c r="DS2" t="s">
-        <v>281</v>
-      </c>
-      <c r="DT2" t="s">
-        <v>283</v>
-      </c>
-      <c r="DU2" t="s">
-        <v>285</v>
-      </c>
-      <c r="DV2" t="s">
-        <v>287</v>
-      </c>
-      <c r="DW2" t="s">
-        <v>235</v>
-      </c>
-      <c r="DX2" t="s">
-        <v>288</v>
-      </c>
-      <c r="DY2" t="s">
-        <v>235</v>
-      </c>
-      <c r="DZ2" t="s">
-        <v>226</v>
-      </c>
-      <c r="EA2" t="s">
-        <v>226</v>
-      </c>
-      <c r="EB2" t="s">
-        <v>226</v>
-      </c>
-      <c r="EC2" t="s">
-        <v>235</v>
-      </c>
-      <c r="ED2" t="s">
-        <v>226</v>
-      </c>
-      <c r="EE2" t="s">
-        <v>226</v>
-      </c>
-      <c r="EF2" t="s">
-        <v>235</v>
-      </c>
-      <c r="EG2" t="s">
-        <v>236</v>
-      </c>
-      <c r="EH2" t="s">
-        <v>289</v>
-      </c>
-      <c r="EI2" t="s">
-        <v>229</v>
-      </c>
-      <c r="EJ2" t="s">
-        <v>226</v>
-      </c>
-      <c r="EK2" t="s">
-        <v>262</v>
-      </c>
-      <c r="EL2" t="s">
-        <v>236</v>
-      </c>
-      <c r="EM2" t="s">
-        <v>262</v>
-      </c>
-      <c r="EN2" t="s">
-        <v>262</v>
-      </c>
-      <c r="EO2" t="s">
-        <v>262</v>
-      </c>
-      <c r="EP2" t="s">
-        <v>262</v>
-      </c>
-      <c r="EQ2" t="s">
-        <v>262</v>
-      </c>
-      <c r="ER2" t="s">
-        <v>290</v>
-      </c>
-      <c r="ES2" t="s">
-        <v>226</v>
-      </c>
-      <c r="ET2" t="s">
-        <v>291</v>
-      </c>
-      <c r="EU2" t="s">
-        <v>226</v>
-      </c>
-      <c r="EV2" t="s">
-        <v>293</v>
-      </c>
-      <c r="EW2" t="s">
-        <v>293</v>
-      </c>
-      <c r="EX2" t="s">
-        <v>226</v>
-      </c>
-      <c r="EY2" t="s">
-        <v>226</v>
-      </c>
-      <c r="EZ2" t="s">
-        <v>226</v>
-      </c>
-      <c r="FA2" t="s">
-        <v>236</v>
-      </c>
-      <c r="FB2" t="s">
-        <v>223</v>
-      </c>
-      <c r="FC2" t="s">
-        <v>226</v>
-      </c>
-      <c r="FD2" t="s">
-        <v>235</v>
-      </c>
-      <c r="FE2" t="s">
-        <v>230</v>
-      </c>
-      <c r="FF2" t="s">
-        <v>226</v>
-      </c>
-      <c r="FG2" t="s">
-        <v>226</v>
-      </c>
-      <c r="FH2" t="s">
-        <v>226</v>
-      </c>
-      <c r="FI2" t="s">
-        <v>230</v>
-      </c>
-      <c r="FJ2" t="s">
-        <v>226</v>
-      </c>
-      <c r="FK2" t="s">
-        <v>226</v>
-      </c>
-      <c r="FL2" t="s">
-        <v>294</v>
-      </c>
-      <c r="FM2" t="s">
-        <v>234</v>
-      </c>
-      <c r="FN2" t="s">
-        <v>226</v>
-      </c>
-      <c r="FO2" t="s">
-        <v>236</v>
-      </c>
-      <c r="FP2" t="s">
-        <v>236</v>
-      </c>
-      <c r="FQ2" t="s">
-        <v>236</v>
-      </c>
-      <c r="FR2" t="s">
-        <v>236</v>
-      </c>
-      <c r="FS2" t="s">
-        <v>236</v>
-      </c>
-      <c r="FT2" t="s">
-        <v>235</v>
-      </c>
-      <c r="FU2" t="s">
-        <v>226</v>
-      </c>
-      <c r="FV2" t="s">
-        <v>295</v>
-      </c>
-      <c r="FW2" t="s">
-        <v>226</v>
-      </c>
-      <c r="FX2" t="s">
-        <v>226</v>
-      </c>
-      <c r="FY2" t="s">
-        <v>296</v>
-      </c>
-      <c r="FZ2" t="s">
-        <v>288</v>
-      </c>
-      <c r="GA2" t="s">
-        <v>226</v>
-      </c>
-      <c r="GB2" t="s">
-        <v>298</v>
-      </c>
-      <c r="GC2" t="s">
-        <v>262</v>
-      </c>
-      <c r="GD2" t="s">
-        <v>299</v>
-      </c>
-      <c r="GE2" t="s">
-        <v>232</v>
-      </c>
-      <c r="GF2" t="s">
-        <v>293</v>
-      </c>
-      <c r="GG2" t="s">
-        <v>299</v>
-      </c>
-      <c r="GH2" t="s">
-        <v>299</v>
-      </c>
-      <c r="GI2" t="s">
-        <v>226</v>
-      </c>
-      <c r="GJ2" t="s">
-        <v>226</v>
-      </c>
-      <c r="GK2" t="s">
-        <v>226</v>
-      </c>
-      <c r="GL2" t="s">
-        <v>226</v>
-      </c>
-      <c r="GM2" t="s">
-        <v>226</v>
-      </c>
-      <c r="GN2" t="s">
-        <v>235</v>
-      </c>
-      <c r="GO2" t="s">
-        <v>300</v>
-      </c>
-      <c r="GP2" t="s">
-        <v>235</v>
-      </c>
-      <c r="GQ2" t="s">
-        <v>301</v>
-      </c>
-      <c r="GR2" t="s">
-        <v>229</v>
-      </c>
-      <c r="GS2" t="s">
-        <v>226</v>
-      </c>
-      <c r="GT2" t="s">
-        <v>281</v>
-      </c>
-      <c r="GU2" t="s">
-        <v>302</v>
-      </c>
-      <c r="GV2" t="s">
-        <v>285</v>
-      </c>
-      <c r="GW2" t="s">
-        <v>305</v>
-      </c>
-      <c r="GX2" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="3" spans="1:206">
-      <c r="A3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B3" t="s">
-        <v>209</v>
-      </c>
-      <c r="C3" t="s">
-        <v>210</v>
-      </c>
-      <c r="D3" t="s">
-        <v>212</v>
-      </c>
-      <c r="E3" t="s">
-        <v>214</v>
-      </c>
-      <c r="F3" t="s">
-        <v>215</v>
-      </c>
-      <c r="G3" t="s">
-        <v>217</v>
-      </c>
-      <c r="H3" t="s">
-        <v>219</v>
-      </c>
-      <c r="I3" t="s">
-        <v>221</v>
-      </c>
-      <c r="J3" t="s">
-        <v>222</v>
-      </c>
-      <c r="K3" t="s">
-        <v>223</v>
-      </c>
-      <c r="L3" t="s">
-        <v>225</v>
-      </c>
-      <c r="M3" t="s">
-        <v>226</v>
-      </c>
-      <c r="N3" t="s">
-        <v>228</v>
-      </c>
-      <c r="O3" t="s">
-        <v>229</v>
-      </c>
-      <c r="P3" t="s">
-        <v>230</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>232</v>
-      </c>
-      <c r="R3" t="s">
-        <v>232</v>
-      </c>
-      <c r="S3" t="s">
-        <v>232</v>
-      </c>
-      <c r="T3" t="s">
-        <v>233</v>
-      </c>
-      <c r="U3" t="s">
-        <v>233</v>
-      </c>
-      <c r="V3" t="s">
-        <v>234</v>
-      </c>
-      <c r="W3" t="s">
-        <v>234</v>
-      </c>
-      <c r="X3" t="s">
-        <v>234</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>235</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>236</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>238</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>226</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>223</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>239</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>241</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>243</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>223</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>226</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>235</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>236</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>226</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>245</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>246</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>230</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>236</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>236</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>236</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>236</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>236</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>236</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>235</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>247</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>248</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>249</v>
-      </c>
-      <c r="AY3" t="s">
-        <v>251</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>230</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>252</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>253</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>235</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>235</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>235</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>235</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>235</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>235</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>235</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>235</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>235</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>235</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>254</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>255</v>
-      </c>
-      <c r="BO3" t="s">
-        <v>226</v>
-      </c>
-      <c r="BP3" t="s">
-        <v>226</v>
-      </c>
-      <c r="BQ3" t="s">
-        <v>256</v>
-      </c>
-      <c r="BR3" t="s">
-        <v>226</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>257</v>
-      </c>
-      <c r="BT3" t="s">
-        <v>226</v>
-      </c>
-      <c r="BU3" t="s">
-        <v>258</v>
-      </c>
-      <c r="BV3" t="s">
-        <v>226</v>
-      </c>
-      <c r="BW3" t="s">
-        <v>260</v>
-      </c>
-      <c r="BX3" t="s">
-        <v>226</v>
-      </c>
-      <c r="BY3" t="s">
-        <v>261</v>
-      </c>
-      <c r="BZ3" t="s">
-        <v>226</v>
-      </c>
-      <c r="CA3" t="s">
-        <v>226</v>
-      </c>
-      <c r="CB3" t="s">
-        <v>263</v>
-      </c>
-      <c r="CC3" t="s">
-        <v>264</v>
-      </c>
-      <c r="CD3" t="s">
-        <v>236</v>
-      </c>
-      <c r="CE3" t="s">
-        <v>253</v>
-      </c>
-      <c r="CF3" t="s">
-        <v>226</v>
-      </c>
-      <c r="CG3" t="s">
-        <v>223</v>
-      </c>
-      <c r="CH3" t="s">
-        <v>226</v>
-      </c>
-      <c r="CI3" t="s">
-        <v>226</v>
-      </c>
-      <c r="CJ3" t="s">
-        <v>223</v>
-      </c>
-      <c r="CK3" t="s">
-        <v>226</v>
-      </c>
-      <c r="CL3" t="s">
-        <v>223</v>
-      </c>
-      <c r="CM3" t="s">
-        <v>223</v>
-      </c>
-      <c r="CN3" t="s">
-        <v>235</v>
-      </c>
-      <c r="CO3" t="s">
-        <v>226</v>
-      </c>
-      <c r="CP3" t="s">
-        <v>226</v>
-      </c>
-      <c r="CQ3" t="s">
-        <v>235</v>
-      </c>
-      <c r="CR3" t="s">
-        <v>226</v>
-      </c>
-      <c r="CS3" t="s">
-        <v>226</v>
-      </c>
-      <c r="CT3" t="s">
-        <v>226</v>
-      </c>
-      <c r="CU3" t="s">
-        <v>226</v>
-      </c>
-      <c r="CV3" t="s">
-        <v>226</v>
-      </c>
-      <c r="CW3" t="s">
-        <v>226</v>
-      </c>
-      <c r="CX3" t="s">
-        <v>226</v>
-      </c>
-      <c r="CY3" t="s">
-        <v>267</v>
-      </c>
-      <c r="CZ3" t="s">
-        <v>226</v>
-      </c>
-      <c r="DA3" t="s">
-        <v>223</v>
-      </c>
-      <c r="DB3" t="s">
-        <v>269</v>
-      </c>
-      <c r="DC3" t="s">
-        <v>270</v>
-      </c>
-      <c r="DD3" t="s">
-        <v>272</v>
-      </c>
-      <c r="DE3" t="s">
-        <v>226</v>
-      </c>
-      <c r="DF3" t="s">
-        <v>274</v>
-      </c>
-      <c r="DG3" t="s">
-        <v>262</v>
-      </c>
-      <c r="DH3" t="s">
-        <v>270</v>
-      </c>
-      <c r="DI3" t="s">
-        <v>261</v>
-      </c>
-      <c r="DJ3" t="s">
-        <v>261</v>
-      </c>
-      <c r="DK3" t="s">
-        <v>275</v>
-      </c>
-      <c r="DL3" t="s">
-        <v>232</v>
-      </c>
-      <c r="DM3" t="s">
-        <v>276</v>
-      </c>
-      <c r="DN3" t="s">
-        <v>276</v>
-      </c>
-      <c r="DO3" t="s">
-        <v>230</v>
-      </c>
-      <c r="DP3" t="s">
-        <v>278</v>
-      </c>
-      <c r="DQ3" t="s">
-        <v>280</v>
-      </c>
-      <c r="DR3" t="s">
-        <v>280</v>
-      </c>
-      <c r="DS3" t="s">
-        <v>282</v>
-      </c>
-      <c r="DT3" t="s">
-        <v>284</v>
-      </c>
-      <c r="DU3" t="s">
-        <v>286</v>
-      </c>
-      <c r="DV3" t="s">
-        <v>287</v>
-      </c>
-      <c r="DW3" t="s">
-        <v>235</v>
-      </c>
-      <c r="DX3" t="s">
-        <v>288</v>
-      </c>
-      <c r="DY3" t="s">
-        <v>235</v>
-      </c>
-      <c r="DZ3" t="s">
-        <v>226</v>
-      </c>
-      <c r="EA3" t="s">
-        <v>226</v>
-      </c>
-      <c r="EB3" t="s">
-        <v>226</v>
-      </c>
-      <c r="EC3" t="s">
-        <v>235</v>
-      </c>
-      <c r="ED3" t="s">
-        <v>226</v>
-      </c>
-      <c r="EE3" t="s">
-        <v>226</v>
-      </c>
-      <c r="EF3" t="s">
-        <v>235</v>
-      </c>
-      <c r="EG3" t="s">
-        <v>236</v>
-      </c>
-      <c r="EH3" t="s">
-        <v>289</v>
-      </c>
-      <c r="EI3" t="s">
-        <v>229</v>
-      </c>
-      <c r="EJ3" t="s">
-        <v>226</v>
-      </c>
-      <c r="EK3" t="s">
-        <v>262</v>
-      </c>
-      <c r="EL3" t="s">
-        <v>236</v>
-      </c>
-      <c r="EM3" t="s">
-        <v>262</v>
-      </c>
-      <c r="EN3" t="s">
-        <v>262</v>
-      </c>
-      <c r="EO3" t="s">
-        <v>262</v>
-      </c>
-      <c r="EP3" t="s">
-        <v>262</v>
-      </c>
-      <c r="EQ3" t="s">
-        <v>262</v>
-      </c>
-      <c r="ER3" t="s">
-        <v>290</v>
-      </c>
-      <c r="ES3" t="s">
-        <v>226</v>
-      </c>
-      <c r="ET3" t="s">
-        <v>292</v>
-      </c>
-      <c r="EU3" t="s">
-        <v>226</v>
-      </c>
-      <c r="EV3" t="s">
-        <v>293</v>
-      </c>
-      <c r="EW3" t="s">
-        <v>293</v>
-      </c>
-      <c r="EX3" t="s">
-        <v>226</v>
-      </c>
-      <c r="EY3" t="s">
-        <v>226</v>
-      </c>
-      <c r="EZ3" t="s">
-        <v>226</v>
-      </c>
-      <c r="FA3" t="s">
-        <v>236</v>
-      </c>
-      <c r="FB3" t="s">
-        <v>223</v>
-      </c>
-      <c r="FC3" t="s">
-        <v>226</v>
-      </c>
-      <c r="FD3" t="s">
-        <v>235</v>
-      </c>
-      <c r="FE3" t="s">
-        <v>230</v>
-      </c>
-      <c r="FF3" t="s">
-        <v>226</v>
-      </c>
-      <c r="FG3" t="s">
-        <v>226</v>
-      </c>
-      <c r="FH3" t="s">
-        <v>226</v>
-      </c>
-      <c r="FI3" t="s">
-        <v>230</v>
-      </c>
-      <c r="FJ3" t="s">
-        <v>226</v>
-      </c>
-      <c r="FK3" t="s">
-        <v>226</v>
-      </c>
-      <c r="FL3" t="s">
-        <v>294</v>
-      </c>
-      <c r="FM3" t="s">
-        <v>234</v>
-      </c>
-      <c r="FN3" t="s">
-        <v>226</v>
-      </c>
-      <c r="FO3" t="s">
-        <v>236</v>
-      </c>
-      <c r="FP3" t="s">
-        <v>236</v>
-      </c>
-      <c r="FQ3" t="s">
-        <v>236</v>
-      </c>
-      <c r="FR3" t="s">
-        <v>236</v>
-      </c>
-      <c r="FS3" t="s">
-        <v>236</v>
-      </c>
-      <c r="FT3" t="s">
-        <v>235</v>
-      </c>
-      <c r="FU3" t="s">
-        <v>226</v>
-      </c>
-      <c r="FV3" t="s">
-        <v>295</v>
-      </c>
-      <c r="FW3" t="s">
-        <v>226</v>
-      </c>
-      <c r="FX3" t="s">
-        <v>226</v>
-      </c>
-      <c r="FY3" t="s">
-        <v>297</v>
-      </c>
-      <c r="FZ3" t="s">
-        <v>288</v>
-      </c>
-      <c r="GA3" t="s">
-        <v>226</v>
-      </c>
-      <c r="GB3" t="s">
-        <v>298</v>
-      </c>
-      <c r="GC3" t="s">
-        <v>262</v>
-      </c>
-      <c r="GD3" t="s">
-        <v>299</v>
-      </c>
-      <c r="GE3" t="s">
-        <v>232</v>
-      </c>
-      <c r="GF3" t="s">
-        <v>293</v>
-      </c>
-      <c r="GG3" t="s">
-        <v>299</v>
-      </c>
-      <c r="GH3" t="s">
-        <v>299</v>
-      </c>
-      <c r="GI3" t="s">
-        <v>226</v>
-      </c>
-      <c r="GJ3" t="s">
-        <v>226</v>
-      </c>
-      <c r="GK3" t="s">
-        <v>226</v>
-      </c>
-      <c r="GL3" t="s">
-        <v>226</v>
-      </c>
-      <c r="GM3" t="s">
-        <v>226</v>
-      </c>
-      <c r="GN3" t="s">
-        <v>235</v>
-      </c>
-      <c r="GO3" t="s">
-        <v>300</v>
-      </c>
-      <c r="GP3" t="s">
-        <v>235</v>
-      </c>
-      <c r="GQ3" t="s">
-        <v>301</v>
-      </c>
-      <c r="GR3" t="s">
-        <v>229</v>
-      </c>
-      <c r="GS3" t="s">
-        <v>226</v>
-      </c>
-      <c r="GT3" t="s">
-        <v>282</v>
-      </c>
-      <c r="GU3" t="s">
-        <v>303</v>
-      </c>
-      <c r="GV3" t="s">
-        <v>304</v>
-      </c>
-      <c r="GW3" t="s">
-        <v>306</v>
-      </c>
-      <c r="GX3" t="s">
-        <v>278</v>
       </c>
     </row>
   </sheetData>
